--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3276,132 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125453497</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78969</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Björnliden, Björnliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>441113</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7171694</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Igenväxande fäbodskog med rikliga förekomster av grova och gamla granar</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -3281,7 +3281,7 @@
         <v>125453497</v>
       </c>
       <c r="B24" t="n">
-        <v>78969</v>
+        <v>79106</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,6 +3397,233 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126010915</v>
+      </c>
+      <c r="B25" t="n">
+        <v>74934</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>440756</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7171142</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126010917</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80072</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>440756</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7171142</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -3281,7 +3281,7 @@
         <v>125453497</v>
       </c>
       <c r="B24" t="n">
-        <v>79126</v>
+        <v>79127</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -3281,7 +3281,7 @@
         <v>125453497</v>
       </c>
       <c r="B24" t="n">
-        <v>79127</v>
+        <v>79131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>126010917</v>
       </c>
       <c r="B26" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -3281,7 +3281,7 @@
         <v>125453497</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>79132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>126010915</v>
       </c>
       <c r="B25" t="n">
-        <v>74934</v>
+        <v>74935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>126010917</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -3402,7 +3402,7 @@
         <v>126010915</v>
       </c>
       <c r="B25" t="n">
-        <v>74935</v>
+        <v>74939</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>126010917</v>
       </c>
       <c r="B26" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -3402,7 +3402,7 @@
         <v>126010915</v>
       </c>
       <c r="B25" t="n">
-        <v>74939</v>
+        <v>74942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>126010917</v>
       </c>
       <c r="B26" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94765696</v>
+        <v>94765690</v>
       </c>
       <c r="B2" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441248.4788995199</v>
+        <v>441200</v>
       </c>
       <c r="R2" t="n">
-        <v>7171515.271754627</v>
+        <v>7171467</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,14 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Högstubbe</t>
+          <t>Grankvistar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,12 +785,7 @@
         <v>94765692</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441224.6578222563</v>
+        <v>441225</v>
       </c>
       <c r="R3" t="n">
-        <v>7171503.736034201</v>
+        <v>7171504</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +850,9 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +884,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94765682</v>
+        <v>112135713</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441117.4783432635</v>
+        <v>441133</v>
       </c>
       <c r="R4" t="n">
-        <v>7171375.549516508</v>
+        <v>7171353</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,38 +966,44 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94765680</v>
+        <v>94765696</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441117.4783432635</v>
+        <v>441248</v>
       </c>
       <c r="R5" t="n">
-        <v>7171375.549516508</v>
+        <v>7171515</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1104,26 +1068,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1135,7 +1084,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,37 +1102,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94765676</v>
+        <v>94765679</v>
       </c>
       <c r="B6" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441052.578587351</v>
+        <v>441117</v>
       </c>
       <c r="R6" t="n">
-        <v>7171281.677941201</v>
+        <v>7171376</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1226,21 +1170,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1252,7 +1186,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Gråal</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,37 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94765684</v>
+        <v>94765689</v>
       </c>
       <c r="B7" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441162.695528558</v>
+        <v>441163</v>
       </c>
       <c r="R7" t="n">
-        <v>7171428.23573951</v>
+        <v>7171428</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1343,21 +1272,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1366,6 +1285,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,15 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94765690</v>
+        <v>94765695</v>
       </c>
       <c r="B8" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>283</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441200.3372216063</v>
+        <v>441248</v>
       </c>
       <c r="R8" t="n">
-        <v>7171466.499340163</v>
+        <v>7171515</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1455,26 +1374,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1486,7 +1390,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Grankvistar</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1504,15 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94765689</v>
+        <v>94765700</v>
       </c>
       <c r="B9" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>498</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1544,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441162.695528558</v>
+        <v>441253</v>
       </c>
       <c r="R9" t="n">
-        <v>7171428.23573951</v>
+        <v>7171528</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1577,19 +1476,14 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,7 +1497,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Grankvistar</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1621,15 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94765700</v>
+        <v>112136779</v>
       </c>
       <c r="B10" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,19 +1544,22 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441253.4459755443</v>
+        <v>441122</v>
       </c>
       <c r="R10" t="n">
-        <v>7171528.030550838</v>
+        <v>7171213</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,27 +1583,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,76 +1597,70 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Grankvistar</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94765698</v>
+        <v>125453497</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Björnliden, Björnliden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441253.4459755443</v>
+        <v>441113</v>
       </c>
       <c r="R11" t="n">
-        <v>7171528.030550838</v>
+        <v>7171694</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,22 +1684,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,60 +1698,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Igenväxande fäbodskog med rikliga förekomster av grova och gamla granar</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94765688</v>
+        <v>94765694</v>
       </c>
       <c r="B12" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1900,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441162.695528558</v>
+        <v>441248</v>
       </c>
       <c r="R12" t="n">
-        <v>7171428.23573951</v>
+        <v>7171515</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1933,21 +1805,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1959,7 +1821,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Grankvist</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1977,15 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94765697</v>
+        <v>94765688</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,21 +1850,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2017,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441253.4459755443</v>
+        <v>441163</v>
       </c>
       <c r="R13" t="n">
-        <v>7171528.030550838</v>
+        <v>7171428</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2050,19 +1907,9 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,37 +1941,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94765679</v>
+        <v>94765680</v>
       </c>
       <c r="B14" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2134,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441117.4783432635</v>
+        <v>441117</v>
       </c>
       <c r="R14" t="n">
-        <v>7171375.549516508</v>
+        <v>7171376</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2167,19 +2009,14 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,7 +2030,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2211,53 +2048,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94765683</v>
+        <v>126010917</v>
       </c>
       <c r="B15" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441117.4783432635</v>
+        <v>440756</v>
       </c>
       <c r="R15" t="n">
-        <v>7171375.549516508</v>
+        <v>7171142</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2281,27 +2116,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,60 +2130,56 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94765694</v>
+        <v>94765677</v>
       </c>
       <c r="B16" t="n">
-        <v>78027</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1353</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2373,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441248.4788995199</v>
+        <v>441069</v>
       </c>
       <c r="R16" t="n">
-        <v>7171515.271754627</v>
+        <v>7171351</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2406,21 +2222,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2432,7 +2238,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Grankvist</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2450,37 +2256,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94765681</v>
+        <v>94765698</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2490,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441117.4783432635</v>
+        <v>441253</v>
       </c>
       <c r="R17" t="n">
-        <v>7171375.549516508</v>
+        <v>7171528</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2523,26 +2324,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2554,7 +2340,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2572,15 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94765671</v>
+        <v>94765676</v>
       </c>
       <c r="B18" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,21 +2369,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>6428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2612,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440823.4934596611</v>
+        <v>441052</v>
       </c>
       <c r="R18" t="n">
-        <v>7171152.011312544</v>
+        <v>7171282</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2645,19 +2426,9 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2689,37 +2460,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94765678</v>
+        <v>94765697</v>
       </c>
       <c r="B19" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2729,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441068.5127237985</v>
+        <v>441253</v>
       </c>
       <c r="R19" t="n">
-        <v>7171350.790711752</v>
+        <v>7171528</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2762,19 +2528,9 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2806,15 +2562,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94765695</v>
+        <v>94765681</v>
       </c>
       <c r="B20" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,21 +2573,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2846,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441248.4788995199</v>
+        <v>441117</v>
       </c>
       <c r="R20" t="n">
-        <v>7171515.271754627</v>
+        <v>7171376</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2879,19 +2630,14 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,7 +2651,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2923,37 +2669,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94765673</v>
+        <v>94765678</v>
       </c>
       <c r="B21" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2963,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440906.4222278903</v>
+        <v>441069</v>
       </c>
       <c r="R21" t="n">
-        <v>7171201.818115615</v>
+        <v>7171351</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2996,19 +2737,9 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3040,15 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94765677</v>
+        <v>94765682</v>
       </c>
       <c r="B22" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3056,21 +2782,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3080,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441068.5127237985</v>
+        <v>441117</v>
       </c>
       <c r="R22" t="n">
-        <v>7171350.790711752</v>
+        <v>7171376</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3113,19 +2839,14 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3139,7 +2860,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3157,56 +2878,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112135713</v>
+        <v>94765683</v>
       </c>
       <c r="B23" t="n">
-        <v>73866</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441134</v>
+        <v>441117</v>
       </c>
       <c r="R23" t="n">
-        <v>7171353</v>
+        <v>7171376</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3230,12 +2943,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3244,85 +2962,71 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gråal</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Alnus incana</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Alnus incana</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125453497</v>
+        <v>94765684</v>
       </c>
       <c r="B24" t="n">
-        <v>79132</v>
+        <v>99456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1249</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnliden, Björnliden, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441113</v>
+        <v>441163</v>
       </c>
       <c r="R24" t="n">
-        <v>7171694</v>
+        <v>7171428</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3346,12 +3050,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3360,90 +3064,66 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Igenväxande fäbodskog med rikliga förekomster av grova och gamla granar</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126010915</v>
+        <v>94765671</v>
       </c>
       <c r="B25" t="n">
-        <v>74942</v>
+        <v>80392</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229654</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440756</v>
+        <v>440823</v>
       </c>
       <c r="R25" t="n">
-        <v>7171142</v>
+        <v>7171152</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3467,12 +3147,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3481,90 +3161,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Gråal</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126010917</v>
+        <v>94765675</v>
       </c>
       <c r="B26" t="n">
-        <v>80084</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>229615</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grynig kolvlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pilophorus cereolus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440756</v>
+        <v>440921</v>
       </c>
       <c r="R26" t="n">
-        <v>7171142</v>
+        <v>7171254</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3588,12 +3249,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På fuktiga klippor invid vattendraget</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3602,27 +3268,243 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112136732</v>
+      </c>
+      <c r="B27" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Styggdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>441122</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7171213</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126010915</v>
+      </c>
+      <c r="B28" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>440756</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7171142</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765692</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112135713</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765696</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765679</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765695</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765700</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112136779</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125453497</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1836,6 +1891,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765694</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765688</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765680</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2151,6 +2221,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010917</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765677</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2355,6 +2435,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765698</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2457,6 +2542,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765676</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2559,6 +2649,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765697</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2666,6 +2761,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765681</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2768,6 +2868,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765678</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2875,6 +2980,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765682</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2982,6 +3092,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765683</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3079,6 +3194,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765684</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3181,6 +3301,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765671</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3283,6 +3408,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765675</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3384,6 +3514,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112136732</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3505,8 +3640,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010915</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2006,48 +2006,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94765680</v>
+        <v>135670792</v>
       </c>
       <c r="B14" t="n">
-        <v>80433</v>
+        <v>75497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1776</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441117</v>
+        <v>440382</v>
       </c>
       <c r="R14" t="n">
-        <v>7171376</v>
+        <v>7171339</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,17 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,33 +2087,28 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765680</t>
+          <t>https://artportalen.se/Sighting/135670792</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126010917</v>
+        <v>94765680</v>
       </c>
       <c r="B15" t="n">
         <v>80433</v>
@@ -2147,22 +2137,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440756</v>
+        <v>441117</v>
       </c>
       <c r="R15" t="n">
-        <v>7171142</v>
+        <v>7171376</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,12 +2173,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,77 +2192,79 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126010917</t>
+          <t>https://artportalen.se/Sighting/94765680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94765677</v>
+        <v>126010917</v>
       </c>
       <c r="B16" t="n">
-        <v>92632</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441069</v>
+        <v>440756</v>
       </c>
       <c r="R16" t="n">
-        <v>7171351</v>
+        <v>7171142</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,12 +2288,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,60 +2302,61 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765677</t>
+          <t>https://artportalen.se/Sighting/126010917</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94765698</v>
+        <v>94765677</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441253</v>
+        <v>441069</v>
       </c>
       <c r="R17" t="n">
-        <v>7171528</v>
+        <v>7171351</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2420,7 +2415,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2437,38 +2432,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765698</t>
+          <t>https://artportalen.se/Sighting/94765677</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94765676</v>
+        <v>94765698</v>
       </c>
       <c r="B18" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441052</v>
+        <v>441253</v>
       </c>
       <c r="R18" t="n">
-        <v>7171282</v>
+        <v>7171528</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2527,7 +2522,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Gråal</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2544,38 +2539,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765676</t>
+          <t>https://artportalen.se/Sighting/94765698</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94765697</v>
+        <v>94765676</v>
       </c>
       <c r="B19" t="n">
-        <v>83307</v>
+        <v>75300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2585,10 +2580,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441253</v>
+        <v>441052</v>
       </c>
       <c r="R19" t="n">
-        <v>7171528</v>
+        <v>7171282</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2634,7 +2629,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gråal</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2651,16 +2646,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765697</t>
+          <t>https://artportalen.se/Sighting/94765676</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94765681</v>
+        <v>94765697</v>
       </c>
       <c r="B20" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,21 +2663,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2692,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441117</v>
+        <v>441253</v>
       </c>
       <c r="R20" t="n">
-        <v>7171376</v>
+        <v>7171528</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2730,11 +2725,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2746,7 +2736,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2763,38 +2753,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765681</t>
+          <t>https://artportalen.se/Sighting/94765697</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94765678</v>
+        <v>94765681</v>
       </c>
       <c r="B21" t="n">
-        <v>79583</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2804,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441069</v>
+        <v>441117</v>
       </c>
       <c r="R21" t="n">
-        <v>7171351</v>
+        <v>7171376</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2842,6 +2832,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2853,7 +2848,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2870,16 +2865,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765678</t>
+          <t>https://artportalen.se/Sighting/94765681</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94765682</v>
+        <v>94765678</v>
       </c>
       <c r="B22" t="n">
-        <v>80461</v>
+        <v>79583</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2887,21 +2882,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2911,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441117</v>
+        <v>441069</v>
       </c>
       <c r="R22" t="n">
-        <v>7171376</v>
+        <v>7171351</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2949,11 +2944,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2965,7 +2955,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2982,16 +2972,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765682</t>
+          <t>https://artportalen.se/Sighting/94765678</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94765683</v>
+        <v>94765682</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,21 +2989,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3094,16 +3084,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765683</t>
+          <t>https://artportalen.se/Sighting/94765682</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94765684</v>
+        <v>94765683</v>
       </c>
       <c r="B24" t="n">
-        <v>99456</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3101,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3125,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441163</v>
+        <v>441117</v>
       </c>
       <c r="R24" t="n">
-        <v>7171428</v>
+        <v>7171376</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3173,6 +3163,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3181,6 +3176,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3196,16 +3196,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765684</t>
+          <t>https://artportalen.se/Sighting/94765683</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94765671</v>
+        <v>94765684</v>
       </c>
       <c r="B25" t="n">
-        <v>80392</v>
+        <v>99456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,21 +3213,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440823</v>
+        <v>441163</v>
       </c>
       <c r="R25" t="n">
-        <v>7171152</v>
+        <v>7171428</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3284,11 +3284,6 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Gråal</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3303,38 +3298,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765671</t>
+          <t>https://artportalen.se/Sighting/94765684</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>94765675</v>
+        <v>94765671</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>80392</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229615</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3344,10 +3339,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440921</v>
+        <v>440823</v>
       </c>
       <c r="R26" t="n">
-        <v>7171254</v>
+        <v>7171152</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3382,11 +3377,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På fuktiga klippor invid vattendraget</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3395,6 +3385,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Gråal</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3410,57 +3405,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765675</t>
+          <t>https://artportalen.se/Sighting/94765671</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112136732</v>
+        <v>94765675</v>
       </c>
       <c r="B27" t="n">
-        <v>75356</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229654</v>
+        <v>229615</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Grynig kolvlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Pilophorus cereolus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441122</v>
+        <v>440921</v>
       </c>
       <c r="R27" t="n">
-        <v>7171213</v>
+        <v>7171254</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3484,12 +3476,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På fuktiga klippor invid vattendraget</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,31 +3495,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112136732</t>
+          <t>https://artportalen.se/Sighting/94765675</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126010915</v>
+        <v>112136732</v>
       </c>
       <c r="B28" t="n">
         <v>75356</v>
@@ -3556,17 +3552,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440756</v>
+        <v>441122</v>
       </c>
       <c r="R28" t="n">
-        <v>7171142</v>
+        <v>7171213</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,12 +3586,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,39 +3604,145 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112136732</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126010915</v>
+      </c>
+      <c r="B29" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>440756</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7171142</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126010915</t>
         </is>
@@ -3675,6 +3777,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -2009,7 +2009,7 @@
         <v>135670792</v>
       </c>
       <c r="B14" t="n">
-        <v>75497</v>
+        <v>75524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2006,48 +2006,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94765680</v>
+        <v>135670792</v>
       </c>
       <c r="B14" t="n">
-        <v>80433</v>
+        <v>75524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1776</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441117</v>
+        <v>440382</v>
       </c>
       <c r="R14" t="n">
-        <v>7171376</v>
+        <v>7171339</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,17 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,33 +2087,28 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765680</t>
+          <t>https://artportalen.se/Sighting/135670792</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126010917</v>
+        <v>94765680</v>
       </c>
       <c r="B15" t="n">
         <v>80433</v>
@@ -2147,22 +2137,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440756</v>
+        <v>441117</v>
       </c>
       <c r="R15" t="n">
-        <v>7171142</v>
+        <v>7171376</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,12 +2173,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,77 +2192,79 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126010917</t>
+          <t>https://artportalen.se/Sighting/94765680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94765677</v>
+        <v>126010917</v>
       </c>
       <c r="B16" t="n">
-        <v>92632</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441069</v>
+        <v>440756</v>
       </c>
       <c r="R16" t="n">
-        <v>7171351</v>
+        <v>7171142</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,12 +2288,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,60 +2302,61 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765677</t>
+          <t>https://artportalen.se/Sighting/126010917</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94765698</v>
+        <v>94765677</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441253</v>
+        <v>441069</v>
       </c>
       <c r="R17" t="n">
-        <v>7171528</v>
+        <v>7171351</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2420,7 +2415,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2437,38 +2432,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765698</t>
+          <t>https://artportalen.se/Sighting/94765677</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94765676</v>
+        <v>94765698</v>
       </c>
       <c r="B18" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441052</v>
+        <v>441253</v>
       </c>
       <c r="R18" t="n">
-        <v>7171282</v>
+        <v>7171528</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2527,7 +2522,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Gråal</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2544,38 +2539,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765676</t>
+          <t>https://artportalen.se/Sighting/94765698</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94765697</v>
+        <v>94765676</v>
       </c>
       <c r="B19" t="n">
-        <v>83307</v>
+        <v>75300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2585,10 +2580,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441253</v>
+        <v>441052</v>
       </c>
       <c r="R19" t="n">
-        <v>7171528</v>
+        <v>7171282</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2634,7 +2629,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gråal</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2651,16 +2646,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765697</t>
+          <t>https://artportalen.se/Sighting/94765676</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94765681</v>
+        <v>94765697</v>
       </c>
       <c r="B20" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,21 +2663,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2692,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441117</v>
+        <v>441253</v>
       </c>
       <c r="R20" t="n">
-        <v>7171376</v>
+        <v>7171528</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2730,11 +2725,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2746,7 +2736,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2763,38 +2753,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765681</t>
+          <t>https://artportalen.se/Sighting/94765697</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94765678</v>
+        <v>94765681</v>
       </c>
       <c r="B21" t="n">
-        <v>79583</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2804,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441069</v>
+        <v>441117</v>
       </c>
       <c r="R21" t="n">
-        <v>7171351</v>
+        <v>7171376</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2842,6 +2832,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2853,7 +2848,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2870,16 +2865,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765678</t>
+          <t>https://artportalen.se/Sighting/94765681</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94765682</v>
+        <v>94765678</v>
       </c>
       <c r="B22" t="n">
-        <v>80461</v>
+        <v>79583</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2887,21 +2882,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2911,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441117</v>
+        <v>441069</v>
       </c>
       <c r="R22" t="n">
-        <v>7171376</v>
+        <v>7171351</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2949,11 +2944,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2965,7 +2955,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2982,16 +2972,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765682</t>
+          <t>https://artportalen.se/Sighting/94765678</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94765683</v>
+        <v>94765682</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,21 +2989,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3094,16 +3084,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765683</t>
+          <t>https://artportalen.se/Sighting/94765682</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94765684</v>
+        <v>94765683</v>
       </c>
       <c r="B24" t="n">
-        <v>99456</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3101,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3125,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441163</v>
+        <v>441117</v>
       </c>
       <c r="R24" t="n">
-        <v>7171428</v>
+        <v>7171376</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3173,6 +3163,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3181,6 +3176,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3196,16 +3196,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765684</t>
+          <t>https://artportalen.se/Sighting/94765683</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94765671</v>
+        <v>94765684</v>
       </c>
       <c r="B25" t="n">
-        <v>80392</v>
+        <v>99456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,21 +3213,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440823</v>
+        <v>441163</v>
       </c>
       <c r="R25" t="n">
-        <v>7171152</v>
+        <v>7171428</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3284,11 +3284,6 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Gråal</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3303,38 +3298,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765671</t>
+          <t>https://artportalen.se/Sighting/94765684</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>94765675</v>
+        <v>94765671</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>80392</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229615</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3344,10 +3339,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440921</v>
+        <v>440823</v>
       </c>
       <c r="R26" t="n">
-        <v>7171254</v>
+        <v>7171152</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3382,11 +3377,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På fuktiga klippor invid vattendraget</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3395,6 +3385,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Gråal</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3410,57 +3405,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765675</t>
+          <t>https://artportalen.se/Sighting/94765671</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112136732</v>
+        <v>94765675</v>
       </c>
       <c r="B27" t="n">
-        <v>75356</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229654</v>
+        <v>229615</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Grynig kolvlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Pilophorus cereolus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441122</v>
+        <v>440921</v>
       </c>
       <c r="R27" t="n">
-        <v>7171213</v>
+        <v>7171254</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3484,12 +3476,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På fuktiga klippor invid vattendraget</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,31 +3495,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112136732</t>
+          <t>https://artportalen.se/Sighting/94765675</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126010915</v>
+        <v>112136732</v>
       </c>
       <c r="B28" t="n">
         <v>75356</v>
@@ -3556,17 +3552,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440756</v>
+        <v>441122</v>
       </c>
       <c r="R28" t="n">
-        <v>7171142</v>
+        <v>7171213</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,12 +3586,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,39 +3604,145 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112136732</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126010915</v>
+      </c>
+      <c r="B29" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>440756</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7171142</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126010915</t>
         </is>
@@ -3675,6 +3777,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -2009,7 +2009,7 @@
         <v>135670792</v>
       </c>
       <c r="B14" t="n">
-        <v>75524</v>
+        <v>75526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1341,48 +1341,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94765695</v>
+        <v>136179860</v>
       </c>
       <c r="B8" t="n">
-        <v>89292</v>
+        <v>78803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441248</v>
+        <v>440534</v>
       </c>
       <c r="R8" t="n">
-        <v>7171515</v>
+        <v>7171049</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,12 +1406,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Koll 10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,58 +1437,53 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765695</t>
+          <t>https://artportalen.se/Sighting/136179860</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94765700</v>
+        <v>94765695</v>
       </c>
       <c r="B9" t="n">
-        <v>79486</v>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441253</v>
+        <v>441248</v>
       </c>
       <c r="R9" t="n">
-        <v>7171528</v>
+        <v>7171515</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1521,11 +1531,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1537,7 +1542,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Grankvistar</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1554,16 +1559,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765700</t>
+          <t>https://artportalen.se/Sighting/94765695</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112136779</v>
+        <v>136173199</v>
       </c>
       <c r="B10" t="n">
-        <v>79486</v>
+        <v>81128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1576,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,17 +1599,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Styggdalsbäcken, Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441122</v>
+        <v>440459</v>
       </c>
       <c r="R10" t="n">
-        <v>7171213</v>
+        <v>7171022</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,12 +1633,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,27 +1651,32 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Frisk, örtrik grannaturskog i mycket brant terräng</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Rashid Kadhim, Alexander Singer, Moa Björnberg Dillner, Uno Skog, Cajsa Björkén, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112136779</t>
+          <t>https://artportalen.se/Sighting/136173199</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125453497</v>
+        <v>94765700</v>
       </c>
       <c r="B11" t="n">
         <v>79486</v>
@@ -1695,22 +1705,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnliden, Björnliden, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441113</v>
+        <v>441253</v>
       </c>
       <c r="R11" t="n">
-        <v>7171694</v>
+        <v>7171528</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,12 +1741,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,92 +1760,79 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Igenväxande fäbodskog med rikliga förekomster av grova och gamla granar</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Grankvistar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125453497</t>
+          <t>https://artportalen.se/Sighting/94765700</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94765694</v>
+        <v>112136779</v>
       </c>
       <c r="B12" t="n">
-        <v>79866</v>
+        <v>79486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1353</v>
+        <v>1249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441248</v>
+        <v>441122</v>
       </c>
       <c r="R12" t="n">
-        <v>7171515</v>
+        <v>7171213</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,12 +1856,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,76 +1870,75 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765694</t>
+          <t>https://artportalen.se/Sighting/112136779</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94765688</v>
+        <v>125453497</v>
       </c>
       <c r="B13" t="n">
-        <v>83312</v>
+        <v>79486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Björnliden, Björnliden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441163</v>
+        <v>441113</v>
       </c>
       <c r="R13" t="n">
-        <v>7171428</v>
+        <v>7171694</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,12 +1962,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,38 +1976,54 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Igenväxande fäbodskog med rikliga förekomster av grova och gamla granar</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765688</t>
+          <t>https://artportalen.se/Sighting/125453497</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135670792</v>
+        <v>136179836</v>
       </c>
       <c r="B14" t="n">
-        <v>75526</v>
+        <v>79603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,37 +2031,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1776</v>
+        <v>1249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brännälven, Brännälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440382</v>
+        <v>440804</v>
       </c>
       <c r="R14" t="n">
-        <v>7171339</v>
+        <v>7171157</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,12 +2085,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,65 +2115,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670792</t>
+          <t>https://artportalen.se/Sighting/136179836</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94765680</v>
+        <v>136179838</v>
       </c>
       <c r="B15" t="n">
-        <v>80433</v>
+        <v>79603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441117</v>
+        <v>440751</v>
       </c>
       <c r="R15" t="n">
-        <v>7171376</v>
+        <v>7171165</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,17 +2197,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,77 +2223,69 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765680</t>
+          <t>https://artportalen.se/Sighting/136179838</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126010917</v>
+        <v>136179876</v>
       </c>
       <c r="B16" t="n">
-        <v>80433</v>
+        <v>79603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440756</v>
+        <v>440444</v>
       </c>
       <c r="R16" t="n">
-        <v>7171142</v>
+        <v>7171044</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,12 +2309,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,61 +2333,55 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126010917</t>
+          <t>https://artportalen.se/Sighting/136179876</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94765677</v>
+        <v>94765694</v>
       </c>
       <c r="B17" t="n">
-        <v>92632</v>
+        <v>79866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441069</v>
+        <v>441248</v>
       </c>
       <c r="R17" t="n">
-        <v>7171351</v>
+        <v>7171515</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2415,7 +2440,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Grankvist</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2432,38 +2457,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765677</t>
+          <t>https://artportalen.se/Sighting/94765694</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94765698</v>
+        <v>94765688</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>83312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441253</v>
+        <v>441163</v>
       </c>
       <c r="R18" t="n">
-        <v>7171528</v>
+        <v>7171428</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2539,54 +2564,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765698</t>
+          <t>https://artportalen.se/Sighting/94765688</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94765676</v>
+        <v>136179865</v>
       </c>
       <c r="B19" t="n">
-        <v>75300</v>
+        <v>83436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6428</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441052</v>
+        <v>440512</v>
       </c>
       <c r="R19" t="n">
-        <v>7171282</v>
+        <v>7171057</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,12 +2635,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,74 +2661,69 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Gråal</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765676</t>
+          <t>https://artportalen.se/Sighting/136179865</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94765697</v>
+        <v>135670792</v>
       </c>
       <c r="B20" t="n">
-        <v>83307</v>
+        <v>75527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1776</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441253</v>
+        <v>440382</v>
       </c>
       <c r="R20" t="n">
-        <v>7171528</v>
+        <v>7171339</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2717,12 +2747,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2733,74 +2763,69 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765697</t>
+          <t>https://artportalen.se/Sighting/135670792</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94765681</v>
+        <v>136179832</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>75527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1776</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441117</v>
+        <v>440778</v>
       </c>
       <c r="R21" t="n">
-        <v>7171376</v>
+        <v>7171278</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2824,17 +2849,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,74 +2875,69 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765681</t>
+          <t>https://artportalen.se/Sighting/136179832</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94765678</v>
+        <v>136179864</v>
       </c>
       <c r="B22" t="n">
-        <v>79583</v>
+        <v>75527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6459</v>
+        <v>1776</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441069</v>
+        <v>440515</v>
       </c>
       <c r="R22" t="n">
-        <v>7171351</v>
+        <v>7171058</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2936,12 +2961,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,74 +2987,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765678</t>
+          <t>https://artportalen.se/Sighting/136179864</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94765682</v>
+        <v>136179866</v>
       </c>
       <c r="B23" t="n">
-        <v>80461</v>
+        <v>75527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1776</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441117</v>
+        <v>440506</v>
       </c>
       <c r="R23" t="n">
-        <v>7171376</v>
+        <v>7171048</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3043,17 +3073,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,74 +3099,69 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765682</t>
+          <t>https://artportalen.se/Sighting/136179866</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94765683</v>
+        <v>136179873</v>
       </c>
       <c r="B24" t="n">
-        <v>80467</v>
+        <v>75527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>1776</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441117</v>
+        <v>440502</v>
       </c>
       <c r="R24" t="n">
-        <v>7171376</v>
+        <v>7171059</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3155,17 +3185,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,74 +3211,69 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765683</t>
+          <t>https://artportalen.se/Sighting/136179873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94765684</v>
+        <v>136179874</v>
       </c>
       <c r="B25" t="n">
-        <v>99456</v>
+        <v>75527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>1776</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441163</v>
+        <v>440479</v>
       </c>
       <c r="R25" t="n">
-        <v>7171428</v>
+        <v>7171050</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3267,12 +3297,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3287,65 +3327,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765684</t>
+          <t>https://artportalen.se/Sighting/136179874</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>94765671</v>
+        <v>136179859</v>
       </c>
       <c r="B26" t="n">
-        <v>80392</v>
+        <v>80323</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>1813</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ros-skivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lecidea roseotincta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Coppins &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440823</v>
+        <v>440540</v>
       </c>
       <c r="R26" t="n">
-        <v>7171152</v>
+        <v>7171050</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3369,12 +3409,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Koll</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3385,58 +3440,53 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Gråal</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765671</t>
+          <t>https://artportalen.se/Sighting/136179859</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94765675</v>
+        <v>94765680</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229615</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3446,10 +3496,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440921</v>
+        <v>441117</v>
       </c>
       <c r="R27" t="n">
-        <v>7171254</v>
+        <v>7171376</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3486,7 +3536,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På fuktiga klippor invid vattendraget</t>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,6 +3547,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3512,38 +3567,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765675</t>
+          <t>https://artportalen.se/Sighting/94765680</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112136732</v>
+        <v>126010917</v>
       </c>
       <c r="B28" t="n">
-        <v>75356</v>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229654</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3552,17 +3607,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441122</v>
+        <v>440756</v>
       </c>
       <c r="R28" t="n">
-        <v>7171213</v>
+        <v>7171142</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3586,12 +3641,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,71 +3659,73 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112136732</t>
+          <t>https://artportalen.se/Sighting/126010917</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126010915</v>
+        <v>136179834</v>
       </c>
       <c r="B29" t="n">
-        <v>75356</v>
+        <v>80560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229654</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440756</v>
+        <v>440810</v>
       </c>
       <c r="R29" t="n">
-        <v>7171142</v>
+        <v>7171208</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3692,12 +3749,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3706,45 +3773,3369 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136179834</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136179862</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>440533</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7171050</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179862</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136179870</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100564</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>440517</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7171043</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179870</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>94765677</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>441069</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7171351</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765677</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>94765698</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>441253</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7171528</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765698</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>94765676</v>
+      </c>
+      <c r="B34" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>441052</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7171282</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Gråal</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765676</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>94765697</v>
+      </c>
+      <c r="B35" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>441253</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7171528</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765697</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136179861</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>440533</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7171050</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Utsn bål På grankvist</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179861</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>94765681</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>441117</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7171376</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765681</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136179833</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>440810</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7171208</v>
+      </c>
+      <c r="S38" t="n">
+        <v>14</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179833</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>94765678</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>441069</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7171351</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765678</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>94765682</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>441117</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7171376</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765682</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>94765683</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>441117</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7171376</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765683</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>94765684</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>441163</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7171428</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765684</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>94765671</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>440823</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7171152</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Gråal</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765671</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136179840</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80509</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>440739</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7171136</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179840</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>94765675</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229615</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grynig kolvlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pilophorus cereolus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Hellb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>440921</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7171254</v>
+      </c>
+      <c r="S45" t="n">
+        <v>50</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På fuktiga klippor invid vattendraget</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94765675</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136179844</v>
+      </c>
+      <c r="B46" t="n">
+        <v>75458</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229651</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglavsknapp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Plectocarpon lichenum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Sommerf.) D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>440655</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7171078</v>
+      </c>
+      <c r="S46" t="n">
+        <v>14</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179844</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136179845</v>
+      </c>
+      <c r="B47" t="n">
+        <v>75460</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229653</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Plectocarpon nephromeum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>440666</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7171114</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179845</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136179846</v>
+      </c>
+      <c r="B48" t="n">
+        <v>75460</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229653</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Plectocarpon nephromeum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>440664</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7171110</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179846</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>112136732</v>
+      </c>
+      <c r="B49" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Styggdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>441122</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7171213</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112136732</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126010915</v>
+      </c>
+      <c r="B50" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>440756</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7171142</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126010915</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136179837</v>
+      </c>
+      <c r="B51" t="n">
+        <v>75462</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>440777</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7171141</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179837</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136179841</v>
+      </c>
+      <c r="B52" t="n">
+        <v>75462</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>440725</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7171132</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179841</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136179851</v>
+      </c>
+      <c r="B53" t="n">
+        <v>75462</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>440592</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7171068</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179851</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136179857</v>
+      </c>
+      <c r="B54" t="n">
+        <v>75462</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>440594</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7171044</v>
+      </c>
+      <c r="S54" t="n">
+        <v>33</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179857</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136179843</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80515</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>440745</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7171143</v>
+      </c>
+      <c r="S55" t="n">
+        <v>8</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179843</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136173210</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79434</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6008463</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cheiromycina petri</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D.Hawksw. &amp; Poelt</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>440645</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7171120</v>
+      </c>
+      <c r="S56" t="n">
+        <v>75</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Frisk, örtrik grannaturskog i mycket brant terräng</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer, Moa Björnberg Dillner, Uno Skog, Cajsa Björkén, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136173210</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136179850</v>
+      </c>
+      <c r="B57" t="n">
+        <v>85450</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>440611</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7171084</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179850</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136179852</v>
+      </c>
+      <c r="B58" t="n">
+        <v>85450</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>440592</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7171068</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179852</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136179854</v>
+      </c>
+      <c r="B59" t="n">
+        <v>85450</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>440616</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7171059</v>
+      </c>
+      <c r="S59" t="n">
+        <v>6</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136179854</t>
         </is>
       </c>
     </row>
@@ -3778,6 +7169,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136173199</v>
+        <v>136198394</v>
       </c>
       <c r="B10" t="n">
-        <v>81128</v>
+        <v>92882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,40 +1576,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440459</v>
+        <v>440628</v>
       </c>
       <c r="R10" t="n">
-        <v>7171022</v>
+        <v>7171061</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,39 +1644,43 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Frisk, örtrik grannaturskog i mycket brant terräng</t>
-        </is>
-      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sälglåga troligtvis. Eller gråal</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer, Moa Björnberg Dillner, Uno Skog, Cajsa Björkén, Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136173199</t>
+          <t>https://artportalen.se/Sighting/136198394</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94765700</v>
+        <v>136173199</v>
       </c>
       <c r="B11" t="n">
-        <v>79486</v>
+        <v>81128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,37 +1688,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441253</v>
+        <v>440459</v>
       </c>
       <c r="R11" t="n">
-        <v>7171528</v>
+        <v>7171022</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,17 +1745,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,35 +1759,36 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Grankvistar</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Frisk, örtrik grannaturskog i mycket brant terräng</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Rashid Kadhim, Alexander Singer, Moa Björnberg Dillner, Uno Skog, Cajsa Björkén, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765700</t>
+          <t>https://artportalen.se/Sighting/136173199</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112136779</v>
+        <v>94765700</v>
       </c>
       <c r="B12" t="n">
         <v>79486</v>
@@ -1817,22 +1817,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441122</v>
+        <v>441253</v>
       </c>
       <c r="R12" t="n">
-        <v>7171213</v>
+        <v>7171528</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,12 +1853,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,31 +1872,35 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Grankvistar</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112136779</t>
+          <t>https://artportalen.se/Sighting/94765700</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125453497</v>
+        <v>112136779</v>
       </c>
       <c r="B13" t="n">
         <v>79486</v>
@@ -1928,17 +1934,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnliden, Björnliden, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441113</v>
+        <v>441122</v>
       </c>
       <c r="R13" t="n">
-        <v>7171694</v>
+        <v>7171213</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,12 +1968,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,50 +1986,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Igenväxande fäbodskog med rikliga förekomster av grova och gamla granar</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125453497</t>
+          <t>https://artportalen.se/Sighting/112136779</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136179836</v>
+        <v>125453497</v>
       </c>
       <c r="B14" t="n">
-        <v>79603</v>
+        <v>79486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,19 +2035,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Björnliden, Björnliden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440804</v>
+        <v>441113</v>
       </c>
       <c r="R14" t="n">
-        <v>7171157</v>
+        <v>7171694</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2085,22 +2074,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:53</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:53</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,30 +2088,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Igenväxande fäbodskog med rikliga förekomster av grova och gamla granar</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179836</t>
+          <t>https://artportalen.se/Sighting/125453497</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136179838</v>
+        <v>136179836</v>
       </c>
       <c r="B15" t="n">
         <v>79603</v>
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440751</v>
+        <v>440804</v>
       </c>
       <c r="R15" t="n">
-        <v>7171165</v>
+        <v>7171157</v>
       </c>
       <c r="S15" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,13 +2238,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179838</t>
+          <t>https://artportalen.se/Sighting/136179836</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136179876</v>
+        <v>136179838</v>
       </c>
       <c r="B16" t="n">
         <v>79603</v>
@@ -2279,13 +2279,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440444</v>
+        <v>440751</v>
       </c>
       <c r="R16" t="n">
-        <v>7171044</v>
+        <v>7171165</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2350,54 +2350,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179876</t>
+          <t>https://artportalen.se/Sighting/136179838</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94765694</v>
+        <v>136179876</v>
       </c>
       <c r="B17" t="n">
-        <v>79866</v>
+        <v>79603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1353</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441248</v>
+        <v>440444</v>
       </c>
       <c r="R17" t="n">
-        <v>7171515</v>
+        <v>7171044</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2421,12 +2421,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,58 +2447,53 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Grankvist</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765694</t>
+          <t>https://artportalen.se/Sighting/136179876</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94765688</v>
+        <v>94765694</v>
       </c>
       <c r="B18" t="n">
-        <v>83312</v>
+        <v>79866</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>1353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441163</v>
+        <v>441248</v>
       </c>
       <c r="R18" t="n">
-        <v>7171428</v>
+        <v>7171515</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2547,7 +2552,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Grankvist</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2564,16 +2569,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765688</t>
+          <t>https://artportalen.se/Sighting/94765694</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136179865</v>
+        <v>94765688</v>
       </c>
       <c r="B19" t="n">
-        <v>83436</v>
+        <v>83312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,17 +2606,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440512</v>
+        <v>441163</v>
       </c>
       <c r="R19" t="n">
-        <v>7171057</v>
+        <v>7171428</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2635,22 +2640,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,69 +2656,74 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179865</t>
+          <t>https://artportalen.se/Sighting/94765688</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135670792</v>
+        <v>136179865</v>
       </c>
       <c r="B20" t="n">
-        <v>75527</v>
+        <v>83436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1776</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brännälven, Brännälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440382</v>
+        <v>440512</v>
       </c>
       <c r="R20" t="n">
-        <v>7171339</v>
+        <v>7171057</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,12 +2747,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,24 +2777,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670792</t>
+          <t>https://artportalen.se/Sighting/136179865</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136179832</v>
+        <v>135670792</v>
       </c>
       <c r="B21" t="n">
         <v>75527</v>
@@ -2815,17 +2825,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Brännälven, Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440778</v>
+        <v>440382</v>
       </c>
       <c r="R21" t="n">
-        <v>7171278</v>
+        <v>7171339</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,22 +2859,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,24 +2879,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179832</t>
+          <t>https://artportalen.se/Sighting/135670792</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136179864</v>
+        <v>136179832</v>
       </c>
       <c r="B22" t="n">
         <v>75527</v>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440515</v>
+        <v>440778</v>
       </c>
       <c r="R22" t="n">
-        <v>7171058</v>
+        <v>7171278</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3002,13 +3002,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179864</t>
+          <t>https://artportalen.se/Sighting/136179832</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136179866</v>
+        <v>136179864</v>
       </c>
       <c r="B23" t="n">
         <v>75527</v>
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440506</v>
+        <v>440515</v>
       </c>
       <c r="R23" t="n">
-        <v>7171048</v>
+        <v>7171058</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,13 +3114,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179866</t>
+          <t>https://artportalen.se/Sighting/136179864</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136179873</v>
+        <v>136179866</v>
       </c>
       <c r="B24" t="n">
         <v>75527</v>
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440502</v>
+        <v>440506</v>
       </c>
       <c r="R24" t="n">
-        <v>7171059</v>
+        <v>7171048</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,13 +3226,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179873</t>
+          <t>https://artportalen.se/Sighting/136179866</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136179874</v>
+        <v>136179873</v>
       </c>
       <c r="B25" t="n">
         <v>75527</v>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440479</v>
+        <v>440502</v>
       </c>
       <c r="R25" t="n">
-        <v>7171050</v>
+        <v>7171059</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,38 +3338,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179874</t>
+          <t>https://artportalen.se/Sighting/136179873</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136179859</v>
+        <v>136179874</v>
       </c>
       <c r="B26" t="n">
-        <v>80323</v>
+        <v>75527</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1813</v>
+        <v>1776</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ros-skivlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lecidea roseotincta</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Coppins &amp; Tønsberg</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440540</v>
+        <v>440479</v>
       </c>
       <c r="R26" t="n">
         <v>7171050</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,12 +3424,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Koll</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,54 +3450,57 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179859</t>
+          <t>https://artportalen.se/Sighting/136179874</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94765680</v>
+        <v>136179859</v>
       </c>
       <c r="B27" t="n">
-        <v>80433</v>
+        <v>80323</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1813</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ros-skivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lecidea roseotincta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Coppins &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441117</v>
+        <v>440540</v>
       </c>
       <c r="R27" t="n">
-        <v>7171376</v>
+        <v>7171050</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3526,17 +3524,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>Två små bålar på slät bark av gråal, ca 30 cm i diameter. Sporer mestadels encelliga, med midja, 11-12x6-7 um, bruna som äldre. Bål K+ magenta. Inga asci funna. Fyndet ska sekvenseras.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3545,35 +3553,50 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765680</t>
+          <t>https://artportalen.se/Sighting/136179859</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126010917</v>
+        <v>94765680</v>
       </c>
       <c r="B28" t="n">
         <v>80433</v>
@@ -3602,22 +3625,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440756</v>
+        <v>441117</v>
       </c>
       <c r="R28" t="n">
-        <v>7171142</v>
+        <v>7171376</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3641,12 +3661,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3655,39 +3680,38 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126010917</t>
+          <t>https://artportalen.se/Sighting/94765680</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136179834</v>
+        <v>126010917</v>
       </c>
       <c r="B29" t="n">
-        <v>80560</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,19 +3737,22 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440810</v>
+        <v>440756</v>
       </c>
       <c r="R29" t="n">
-        <v>7171208</v>
+        <v>7171142</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3749,22 +3776,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,30 +3790,36 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179834</t>
+          <t>https://artportalen.se/Sighting/126010917</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136179862</v>
+        <v>136179834</v>
       </c>
       <c r="B30" t="n">
         <v>80560</v>
@@ -3831,10 +3854,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440533</v>
+        <v>440810</v>
       </c>
       <c r="R30" t="n">
-        <v>7171050</v>
+        <v>7171208</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3866,7 +3889,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3876,12 +3899,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3892,21 +3910,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3922,38 +3925,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179862</t>
+          <t>https://artportalen.se/Sighting/136179834</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136179870</v>
+        <v>136179862</v>
       </c>
       <c r="B31" t="n">
-        <v>100564</v>
+        <v>80560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,10 +3966,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440517</v>
+        <v>440533</v>
       </c>
       <c r="R31" t="n">
-        <v>7171043</v>
+        <v>7171050</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3998,7 +4001,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +4011,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4019,6 +4027,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4034,16 +4057,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179870</t>
+          <t>https://artportalen.se/Sighting/136179862</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>94765677</v>
+        <v>136179870</v>
       </c>
       <c r="B32" t="n">
-        <v>92632</v>
+        <v>100564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4051,37 +4074,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>2082</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441069</v>
+        <v>440517</v>
       </c>
       <c r="R32" t="n">
-        <v>7171351</v>
+        <v>7171043</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4105,12 +4128,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4121,58 +4154,53 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765677</t>
+          <t>https://artportalen.se/Sighting/136179870</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>94765698</v>
+        <v>94765677</v>
       </c>
       <c r="B33" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4182,10 +4210,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441253</v>
+        <v>441069</v>
       </c>
       <c r="R33" t="n">
-        <v>7171528</v>
+        <v>7171351</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4231,7 +4259,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4248,38 +4276,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765698</t>
+          <t>https://artportalen.se/Sighting/94765677</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>94765676</v>
+        <v>94765698</v>
       </c>
       <c r="B34" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441052</v>
+        <v>441253</v>
       </c>
       <c r="R34" t="n">
-        <v>7171282</v>
+        <v>7171528</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4338,7 +4366,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Gråal</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4355,38 +4383,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765676</t>
+          <t>https://artportalen.se/Sighting/94765698</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>94765697</v>
+        <v>94765676</v>
       </c>
       <c r="B35" t="n">
-        <v>83307</v>
+        <v>75300</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4396,10 +4424,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441253</v>
+        <v>441052</v>
       </c>
       <c r="R35" t="n">
-        <v>7171528</v>
+        <v>7171282</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4445,7 +4473,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gråal</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4462,54 +4490,54 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765697</t>
+          <t>https://artportalen.se/Sighting/94765676</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136179861</v>
+        <v>94765697</v>
       </c>
       <c r="B36" t="n">
-        <v>78802</v>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440533</v>
+        <v>441253</v>
       </c>
       <c r="R36" t="n">
-        <v>7171050</v>
+        <v>7171528</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4533,27 +4561,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Utsn bål På grankvist</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4564,69 +4577,74 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179861</t>
+          <t>https://artportalen.se/Sighting/94765697</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>94765681</v>
+        <v>136179861</v>
       </c>
       <c r="B37" t="n">
-        <v>80432</v>
+        <v>78802</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6443</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441117</v>
+        <v>440533</v>
       </c>
       <c r="R37" t="n">
-        <v>7171376</v>
+        <v>7171050</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4650,17 +4668,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>Utsn bål På grankvist</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4671,36 +4699,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765681</t>
+          <t>https://artportalen.se/Sighting/136179861</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136179833</v>
+        <v>94765681</v>
       </c>
       <c r="B38" t="n">
-        <v>80559</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4728,17 +4751,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440810</v>
+        <v>441117</v>
       </c>
       <c r="R38" t="n">
-        <v>7171208</v>
+        <v>7171376</v>
       </c>
       <c r="S38" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,22 +4785,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4788,69 +4806,74 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179833</t>
+          <t>https://artportalen.se/Sighting/94765681</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>94765678</v>
+        <v>136179833</v>
       </c>
       <c r="B39" t="n">
-        <v>79583</v>
+        <v>80559</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441069</v>
+        <v>440810</v>
       </c>
       <c r="R39" t="n">
-        <v>7171351</v>
+        <v>7171208</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4874,12 +4897,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,36 +4923,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765678</t>
+          <t>https://artportalen.se/Sighting/136179833</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>94765682</v>
+        <v>94765678</v>
       </c>
       <c r="B40" t="n">
-        <v>80461</v>
+        <v>79583</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4927,21 +4955,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4951,10 +4979,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441117</v>
+        <v>441069</v>
       </c>
       <c r="R40" t="n">
-        <v>7171376</v>
+        <v>7171351</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4989,11 +5017,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5005,7 +5028,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5022,16 +5045,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765682</t>
+          <t>https://artportalen.se/Sighting/94765678</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>94765683</v>
+        <v>94765682</v>
       </c>
       <c r="B41" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5039,21 +5062,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5134,16 +5157,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765683</t>
+          <t>https://artportalen.se/Sighting/94765682</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>94765684</v>
+        <v>94765683</v>
       </c>
       <c r="B42" t="n">
-        <v>99456</v>
+        <v>80467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5151,21 +5174,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219880</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5175,10 +5198,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441163</v>
+        <v>441117</v>
       </c>
       <c r="R42" t="n">
-        <v>7171428</v>
+        <v>7171376</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5213,6 +5236,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5221,6 +5249,11 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5236,16 +5269,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765684</t>
+          <t>https://artportalen.se/Sighting/94765683</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>94765671</v>
+        <v>94765684</v>
       </c>
       <c r="B43" t="n">
-        <v>80392</v>
+        <v>99456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5253,21 +5286,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>219880</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5277,10 +5310,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440823</v>
+        <v>441163</v>
       </c>
       <c r="R43" t="n">
-        <v>7171152</v>
+        <v>7171428</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5324,11 +5357,6 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Gråal</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5343,16 +5371,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765671</t>
+          <t>https://artportalen.se/Sighting/94765684</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136179840</v>
+        <v>94765671</v>
       </c>
       <c r="B44" t="n">
-        <v>80509</v>
+        <v>80392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5380,17 +5408,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440739</v>
+        <v>440823</v>
       </c>
       <c r="R44" t="n">
-        <v>7171136</v>
+        <v>7171152</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5414,22 +5442,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5440,69 +5458,74 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Gråal</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179840</t>
+          <t>https://artportalen.se/Sighting/94765671</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>94765675</v>
+        <v>136179840</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>80509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229615</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440921</v>
+        <v>440739</v>
       </c>
       <c r="R45" t="n">
-        <v>7171254</v>
+        <v>7171136</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5526,17 +5549,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På fuktiga klippor invid vattendraget</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5551,65 +5579,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765675</t>
+          <t>https://artportalen.se/Sighting/136179840</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136179844</v>
+        <v>94765675</v>
       </c>
       <c r="B46" t="n">
-        <v>75458</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229651</v>
+        <v>229615</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Grynig kolvlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Pilophorus cereolus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440655</v>
+        <v>440921</v>
       </c>
       <c r="R46" t="n">
-        <v>7171078</v>
+        <v>7171254</v>
       </c>
       <c r="S46" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5633,22 +5661,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På fuktiga klippor invid vattendraget</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5663,49 +5686,49 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179844</t>
+          <t>https://artportalen.se/Sighting/94765675</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136179845</v>
+        <v>136179844</v>
       </c>
       <c r="B47" t="n">
-        <v>75460</v>
+        <v>75458</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229653</v>
+        <v>229651</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5715,13 +5738,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440666</v>
+        <v>440655</v>
       </c>
       <c r="R47" t="n">
-        <v>7171114</v>
+        <v>7171078</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5750,7 +5773,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5760,12 +5783,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5791,54 +5809,54 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179845</t>
+          <t>https://artportalen.se/Sighting/136179844</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136179846</v>
+        <v>136198395</v>
       </c>
       <c r="B48" t="n">
-        <v>75460</v>
+        <v>75458</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229653</v>
+        <v>229651</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440664</v>
+        <v>440586</v>
       </c>
       <c r="R48" t="n">
-        <v>7171110</v>
+        <v>7171052</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5865,26 +5883,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5894,30 +5897,45 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr"/>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179846</t>
+          <t>https://artportalen.se/Sighting/136198395</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112136732</v>
+        <v>136179845</v>
       </c>
       <c r="B49" t="n">
-        <v>75356</v>
+        <v>75460</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5925,40 +5943,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229654</v>
+        <v>229653</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441122</v>
+        <v>440666</v>
       </c>
       <c r="R49" t="n">
-        <v>7171213</v>
+        <v>7171114</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5982,12 +5997,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,34 +6026,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112136732</t>
+          <t>https://artportalen.se/Sighting/136179845</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126010915</v>
+        <v>136179846</v>
       </c>
       <c r="B50" t="n">
-        <v>75356</v>
+        <v>75460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6031,40 +6060,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229654</v>
+        <v>229653</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440756</v>
+        <v>440664</v>
       </c>
       <c r="R50" t="n">
-        <v>7171142</v>
+        <v>7171110</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6088,12 +6114,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6102,54 +6143,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126010915</t>
+          <t>https://artportalen.se/Sighting/136179846</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136179837</v>
+        <v>112136732</v>
       </c>
       <c r="B51" t="n">
-        <v>75462</v>
+        <v>75356</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6175,19 +6195,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440777</v>
+        <v>441122</v>
       </c>
       <c r="R51" t="n">
-        <v>7171141</v>
+        <v>7171213</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6211,22 +6234,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6235,33 +6248,34 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179837</t>
+          <t>https://artportalen.se/Sighting/112136732</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136179841</v>
+        <v>126010915</v>
       </c>
       <c r="B52" t="n">
-        <v>75462</v>
+        <v>75356</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,19 +6301,22 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440725</v>
+        <v>440756</v>
       </c>
       <c r="R52" t="n">
-        <v>7171132</v>
+        <v>7171142</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6323,22 +6340,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6347,30 +6354,51 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179841</t>
+          <t>https://artportalen.se/Sighting/126010915</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136179851</v>
+        <v>136179837</v>
       </c>
       <c r="B53" t="n">
         <v>75462</v>
@@ -6405,10 +6433,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440592</v>
+        <v>440777</v>
       </c>
       <c r="R53" t="n">
-        <v>7171068</v>
+        <v>7171141</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6440,7 +6468,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6450,7 +6478,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6476,13 +6504,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179851</t>
+          <t>https://artportalen.se/Sighting/136179837</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136179857</v>
+        <v>136179841</v>
       </c>
       <c r="B54" t="n">
         <v>75462</v>
@@ -6517,13 +6545,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440594</v>
+        <v>440725</v>
       </c>
       <c r="R54" t="n">
-        <v>7171044</v>
+        <v>7171132</v>
       </c>
       <c r="S54" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6552,7 +6580,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6562,7 +6590,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6588,38 +6616,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179857</t>
+          <t>https://artportalen.se/Sighting/136179841</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136179843</v>
+        <v>136179851</v>
       </c>
       <c r="B55" t="n">
-        <v>80515</v>
+        <v>75462</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229748</v>
+        <v>229654</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6629,13 +6657,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440745</v>
+        <v>440592</v>
       </c>
       <c r="R55" t="n">
-        <v>7171143</v>
+        <v>7171068</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6664,7 +6692,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6674,7 +6702,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6700,52 +6728,54 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179843</t>
+          <t>https://artportalen.se/Sighting/136179851</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136173210</v>
+        <v>136179857</v>
       </c>
       <c r="B56" t="n">
-        <v>79434</v>
+        <v>75462</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6008463</v>
+        <v>229654</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cheiromycina petri</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>D.Hawksw. &amp; Poelt</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440645</v>
+        <v>440594</v>
       </c>
       <c r="R56" t="n">
-        <v>7171120</v>
+        <v>7171044</v>
       </c>
       <c r="S56" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6772,67 +6802,76 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Frisk, örtrik grannaturskog i mycket brant terräng</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer, Moa Björnberg Dillner, Uno Skog, Cajsa Björkén, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136173210</t>
+          <t>https://artportalen.se/Sighting/136179857</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136179850</v>
+        <v>136179843</v>
       </c>
       <c r="B57" t="n">
-        <v>85450</v>
+        <v>80515</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6331313</v>
+        <v>229748</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Roselliniella nephromatis</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6842,13 +6881,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440611</v>
+        <v>440745</v>
       </c>
       <c r="R57" t="n">
-        <v>7171084</v>
+        <v>7171143</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6877,7 +6916,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6887,12 +6926,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6901,7 +6935,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6919,13 +6952,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179850</t>
+          <t>https://artportalen.se/Sighting/136179843</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136179852</v>
+        <v>136179850</v>
       </c>
       <c r="B58" t="n">
         <v>85450</v>
@@ -6955,13 +6988,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440592</v>
+        <v>440611</v>
       </c>
       <c r="R58" t="n">
-        <v>7171068</v>
+        <v>7171084</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6990,7 +7023,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7000,7 +7033,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7027,13 +7065,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179852</t>
+          <t>https://artportalen.se/Sighting/136179850</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136179854</v>
+        <v>136179852</v>
       </c>
       <c r="B59" t="n">
         <v>85450</v>
@@ -7063,13 +7101,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440616</v>
+        <v>440592</v>
       </c>
       <c r="R59" t="n">
-        <v>7171059</v>
+        <v>7171068</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7098,7 +7136,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7108,7 +7146,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7135,7 +7173,217 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136179852</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136179854</v>
+      </c>
+      <c r="B60" t="n">
+        <v>85450</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Brännälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>440616</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7171059</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136179854</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136202366</v>
+      </c>
+      <c r="B61" t="n">
+        <v>85450</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>440594</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7171053</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136202366</t>
         </is>
       </c>
     </row>
@@ -7199,6 +7447,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136227066</v>
       </c>
       <c r="B4" t="n">
-        <v>79525</v>
+        <v>79526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136203730</v>
       </c>
       <c r="B9" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136179860</v>
       </c>
       <c r="B11" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92883</v>
+        <v>92884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136173199</v>
       </c>
       <c r="B14" t="n">
-        <v>81128</v>
+        <v>81129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135671126</v>
       </c>
       <c r="B19" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>136179836</v>
       </c>
       <c r="B20" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136179838</v>
       </c>
       <c r="B21" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136179876</v>
       </c>
       <c r="B22" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136227090</v>
       </c>
       <c r="B23" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136240857</v>
       </c>
       <c r="B24" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136179865</v>
       </c>
       <c r="B27" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136227071</v>
       </c>
       <c r="B28" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136240851</v>
       </c>
       <c r="B29" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136240854</v>
       </c>
       <c r="B30" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>136240856</v>
       </c>
       <c r="B31" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>135670792</v>
       </c>
       <c r="B32" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>135671135</v>
       </c>
       <c r="B33" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>136179832</v>
       </c>
       <c r="B34" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136179864</v>
       </c>
       <c r="B35" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>136179866</v>
       </c>
       <c r="B36" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>136179873</v>
       </c>
       <c r="B37" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136179874</v>
       </c>
       <c r="B38" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136219638</v>
       </c>
       <c r="B39" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136219642</v>
       </c>
       <c r="B40" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>136219649</v>
       </c>
       <c r="B41" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136227067</v>
       </c>
       <c r="B42" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>136240852</v>
       </c>
       <c r="B43" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136240863</v>
       </c>
       <c r="B44" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136240866</v>
       </c>
       <c r="B45" t="n">
-        <v>75527</v>
+        <v>75528</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>136179859</v>
       </c>
       <c r="B46" t="n">
-        <v>80323</v>
+        <v>80324</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>136179834</v>
       </c>
       <c r="B49" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>136179862</v>
       </c>
       <c r="B50" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136227069</v>
       </c>
       <c r="B51" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100565</v>
+        <v>100566</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100565</v>
+        <v>100566</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100565</v>
+        <v>100566</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100565</v>
+        <v>100566</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>136225509</v>
       </c>
       <c r="B57" t="n">
-        <v>87657</v>
+        <v>87658</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>136179861</v>
       </c>
       <c r="B61" t="n">
-        <v>78802</v>
+        <v>78803</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>136179833</v>
       </c>
       <c r="B63" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>136227075</v>
       </c>
       <c r="B64" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136219658</v>
       </c>
       <c r="B67" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>136227091</v>
       </c>
       <c r="B69" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>136227078</v>
       </c>
       <c r="B71" t="n">
-        <v>85369</v>
+        <v>85370</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>136179840</v>
       </c>
       <c r="B73" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136240864</v>
       </c>
       <c r="B74" t="n">
-        <v>80579</v>
+        <v>80580</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>136179844</v>
       </c>
       <c r="B76" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>136198395</v>
       </c>
       <c r="B77" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>136203727</v>
       </c>
       <c r="B78" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>136227076</v>
       </c>
       <c r="B79" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>136227082</v>
       </c>
       <c r="B80" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>136227084</v>
       </c>
       <c r="B81" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>136227086</v>
       </c>
       <c r="B82" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>136240855</v>
       </c>
       <c r="B83" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>136240860</v>
       </c>
       <c r="B84" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>136179845</v>
       </c>
       <c r="B85" t="n">
-        <v>75460</v>
+        <v>75461</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>136179846</v>
       </c>
       <c r="B86" t="n">
-        <v>75460</v>
+        <v>75461</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>136179837</v>
       </c>
       <c r="B89" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>136179841</v>
       </c>
       <c r="B90" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>136179851</v>
       </c>
       <c r="B91" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>136179857</v>
       </c>
       <c r="B92" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136203725</v>
       </c>
       <c r="B93" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>136227070</v>
       </c>
       <c r="B94" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>136227073</v>
       </c>
       <c r="B95" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>136240853</v>
       </c>
       <c r="B96" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>136240858</v>
       </c>
       <c r="B97" t="n">
-        <v>75462</v>
+        <v>75463</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>136179843</v>
       </c>
       <c r="B98" t="n">
-        <v>80515</v>
+        <v>80516</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>136219661</v>
       </c>
       <c r="B99" t="n">
-        <v>80515</v>
+        <v>80516</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>136219654</v>
       </c>
       <c r="B100" t="n">
-        <v>79916</v>
+        <v>79917</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136227089</v>
       </c>
       <c r="B101" t="n">
-        <v>79916</v>
+        <v>79917</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>136240859</v>
       </c>
       <c r="B102" t="n">
-        <v>79916</v>
+        <v>79917</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>136179850</v>
       </c>
       <c r="B103" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136179852</v>
       </c>
       <c r="B104" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>136179854</v>
       </c>
       <c r="B105" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>136202366</v>
       </c>
       <c r="B106" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>136227080</v>
       </c>
       <c r="B107" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136227081</v>
       </c>
       <c r="B108" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>136227083</v>
       </c>
       <c r="B109" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>136227085</v>
       </c>
       <c r="B110" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>136227088</v>
       </c>
       <c r="B111" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136227066</v>
       </c>
       <c r="B4" t="n">
-        <v>79526</v>
+        <v>79530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136203730</v>
       </c>
       <c r="B9" t="n">
-        <v>83423</v>
+        <v>83427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136179860</v>
       </c>
       <c r="B11" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92884</v>
+        <v>92890</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136173199</v>
       </c>
       <c r="B14" t="n">
-        <v>81129</v>
+        <v>81133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135671126</v>
       </c>
       <c r="B19" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>136179836</v>
       </c>
       <c r="B20" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136179838</v>
       </c>
       <c r="B21" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136179876</v>
       </c>
       <c r="B22" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136227090</v>
       </c>
       <c r="B23" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136240857</v>
       </c>
       <c r="B24" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136179865</v>
       </c>
       <c r="B27" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136227071</v>
       </c>
       <c r="B28" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136240851</v>
       </c>
       <c r="B29" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136240854</v>
       </c>
       <c r="B30" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>136240856</v>
       </c>
       <c r="B31" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>135670792</v>
       </c>
       <c r="B32" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>135671135</v>
       </c>
       <c r="B33" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>136179832</v>
       </c>
       <c r="B34" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136179864</v>
       </c>
       <c r="B35" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>136179866</v>
       </c>
       <c r="B36" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>136179873</v>
       </c>
       <c r="B37" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136179874</v>
       </c>
       <c r="B38" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136219638</v>
       </c>
       <c r="B39" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136219642</v>
       </c>
       <c r="B40" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>136219649</v>
       </c>
       <c r="B41" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136227067</v>
       </c>
       <c r="B42" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>136240852</v>
       </c>
       <c r="B43" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136240863</v>
       </c>
       <c r="B44" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136240866</v>
       </c>
       <c r="B45" t="n">
-        <v>75528</v>
+        <v>75532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>136179859</v>
       </c>
       <c r="B46" t="n">
-        <v>80324</v>
+        <v>80328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>136179834</v>
       </c>
       <c r="B49" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>136179862</v>
       </c>
       <c r="B50" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136227069</v>
       </c>
       <c r="B51" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100566</v>
+        <v>100572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100566</v>
+        <v>100572</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100566</v>
+        <v>100572</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100566</v>
+        <v>100572</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>136225509</v>
       </c>
       <c r="B57" t="n">
-        <v>87658</v>
+        <v>87664</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>136179861</v>
       </c>
       <c r="B61" t="n">
-        <v>78803</v>
+        <v>78807</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>136179833</v>
       </c>
       <c r="B63" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>136227075</v>
       </c>
       <c r="B64" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136219658</v>
       </c>
       <c r="B67" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>136227091</v>
       </c>
       <c r="B69" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>136227078</v>
       </c>
       <c r="B71" t="n">
-        <v>85370</v>
+        <v>85374</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>136179840</v>
       </c>
       <c r="B73" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136240864</v>
       </c>
       <c r="B74" t="n">
-        <v>80580</v>
+        <v>80584</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>136179844</v>
       </c>
       <c r="B76" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>136198395</v>
       </c>
       <c r="B77" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>136203727</v>
       </c>
       <c r="B78" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>136227076</v>
       </c>
       <c r="B79" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>136227082</v>
       </c>
       <c r="B80" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>136227084</v>
       </c>
       <c r="B81" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>136227086</v>
       </c>
       <c r="B82" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>136240855</v>
       </c>
       <c r="B83" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>136240860</v>
       </c>
       <c r="B84" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>136179845</v>
       </c>
       <c r="B85" t="n">
-        <v>75461</v>
+        <v>75465</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>136179846</v>
       </c>
       <c r="B86" t="n">
-        <v>75461</v>
+        <v>75465</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>136179837</v>
       </c>
       <c r="B89" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>136179841</v>
       </c>
       <c r="B90" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>136179851</v>
       </c>
       <c r="B91" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>136179857</v>
       </c>
       <c r="B92" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136203725</v>
       </c>
       <c r="B93" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>136227070</v>
       </c>
       <c r="B94" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>136227073</v>
       </c>
       <c r="B95" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>136240853</v>
       </c>
       <c r="B96" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>136240858</v>
       </c>
       <c r="B97" t="n">
-        <v>75463</v>
+        <v>75467</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>136179843</v>
       </c>
       <c r="B98" t="n">
-        <v>80516</v>
+        <v>80520</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>136219661</v>
       </c>
       <c r="B99" t="n">
-        <v>80516</v>
+        <v>80520</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>136219654</v>
       </c>
       <c r="B100" t="n">
-        <v>79917</v>
+        <v>79921</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136227089</v>
       </c>
       <c r="B101" t="n">
-        <v>79917</v>
+        <v>79921</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>136240859</v>
       </c>
       <c r="B102" t="n">
-        <v>79917</v>
+        <v>79921</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>136179850</v>
       </c>
       <c r="B103" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136179852</v>
       </c>
       <c r="B104" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>136179854</v>
       </c>
       <c r="B105" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>136202366</v>
       </c>
       <c r="B106" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>136227080</v>
       </c>
       <c r="B107" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136227081</v>
       </c>
       <c r="B108" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>136227083</v>
       </c>
       <c r="B109" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>136227085</v>
       </c>
       <c r="B110" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>136227088</v>
       </c>
       <c r="B111" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136227066</v>
       </c>
       <c r="B4" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1461,7 +1461,7 @@
         <v>136203730</v>
       </c>
       <c r="B9" t="n">
-        <v>83427</v>
+        <v>83428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136179860</v>
       </c>
       <c r="B11" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92890</v>
+        <v>92891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136173199</v>
       </c>
       <c r="B14" t="n">
-        <v>81133</v>
+        <v>81134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135671126</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>136179836</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136179838</v>
       </c>
       <c r="B21" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136179876</v>
       </c>
       <c r="B22" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136227090</v>
       </c>
       <c r="B23" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
         <v>136240857</v>
       </c>
       <c r="B24" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136179865</v>
       </c>
       <c r="B27" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136227071</v>
       </c>
       <c r="B28" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
         <v>136240851</v>
       </c>
       <c r="B29" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136240854</v>
       </c>
       <c r="B30" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>136240856</v>
       </c>
       <c r="B31" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>135670792</v>
       </c>
       <c r="B32" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>135671135</v>
       </c>
       <c r="B33" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>136179832</v>
       </c>
       <c r="B34" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136179864</v>
       </c>
       <c r="B35" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>136179866</v>
       </c>
       <c r="B36" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>136179873</v>
       </c>
       <c r="B37" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136179874</v>
       </c>
       <c r="B38" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136219638</v>
       </c>
       <c r="B39" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136219642</v>
       </c>
       <c r="B40" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>136219649</v>
       </c>
       <c r="B41" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136227067</v>
       </c>
       <c r="B42" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5275,7 +5275,7 @@
         <v>136240852</v>
       </c>
       <c r="B43" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136240863</v>
       </c>
       <c r="B44" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136240866</v>
       </c>
       <c r="B45" t="n">
-        <v>75532</v>
+        <v>75533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>136179859</v>
       </c>
       <c r="B46" t="n">
-        <v>80328</v>
+        <v>80329</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>136179834</v>
       </c>
       <c r="B49" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>136179862</v>
       </c>
       <c r="B50" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136227069</v>
       </c>
       <c r="B51" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100572</v>
+        <v>100573</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100572</v>
+        <v>100573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100572</v>
+        <v>100573</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100572</v>
+        <v>100573</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>136225509</v>
       </c>
       <c r="B57" t="n">
-        <v>87664</v>
+        <v>87665</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>136179861</v>
       </c>
       <c r="B61" t="n">
-        <v>78807</v>
+        <v>78808</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>136179833</v>
       </c>
       <c r="B63" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>136227075</v>
       </c>
       <c r="B64" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7990,7 +7990,7 @@
         <v>136219658</v>
       </c>
       <c r="B67" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>136227091</v>
       </c>
       <c r="B69" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
         <v>136227078</v>
       </c>
       <c r="B71" t="n">
-        <v>85374</v>
+        <v>85375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8667,7 +8667,7 @@
         <v>136179840</v>
       </c>
       <c r="B73" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136240864</v>
       </c>
       <c r="B74" t="n">
-        <v>80584</v>
+        <v>80585</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>136179844</v>
       </c>
       <c r="B76" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>136198395</v>
       </c>
       <c r="B77" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>136203727</v>
       </c>
       <c r="B78" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>136227076</v>
       </c>
       <c r="B79" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9455,7 +9455,7 @@
         <v>136227082</v>
       </c>
       <c r="B80" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
         <v>136227084</v>
       </c>
       <c r="B81" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
         <v>136227086</v>
       </c>
       <c r="B82" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9791,7 +9791,7 @@
         <v>136240855</v>
       </c>
       <c r="B83" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>136240860</v>
       </c>
       <c r="B84" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>136179845</v>
       </c>
       <c r="B85" t="n">
-        <v>75465</v>
+        <v>75466</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>136179846</v>
       </c>
       <c r="B86" t="n">
-        <v>75465</v>
+        <v>75466</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>136179837</v>
       </c>
       <c r="B89" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>136179841</v>
       </c>
       <c r="B90" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>136179851</v>
       </c>
       <c r="B91" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>136179857</v>
       </c>
       <c r="B92" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136203725</v>
       </c>
       <c r="B93" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>136227070</v>
       </c>
       <c r="B94" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
         <v>136227073</v>
       </c>
       <c r="B95" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11273,7 +11273,7 @@
         <v>136240853</v>
       </c>
       <c r="B96" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>136240858</v>
       </c>
       <c r="B97" t="n">
-        <v>75467</v>
+        <v>75468</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>136179843</v>
       </c>
       <c r="B98" t="n">
-        <v>80520</v>
+        <v>80521</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>136219661</v>
       </c>
       <c r="B99" t="n">
-        <v>80520</v>
+        <v>80521</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>136219654</v>
       </c>
       <c r="B100" t="n">
-        <v>79921</v>
+        <v>79922</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136227089</v>
       </c>
       <c r="B101" t="n">
-        <v>79921</v>
+        <v>79922</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11967,7 +11967,7 @@
         <v>136240859</v>
       </c>
       <c r="B102" t="n">
-        <v>79921</v>
+        <v>79922</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>136179850</v>
       </c>
       <c r="B103" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136179852</v>
       </c>
       <c r="B104" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>136179854</v>
       </c>
       <c r="B105" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>136202366</v>
       </c>
       <c r="B106" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>136227080</v>
       </c>
       <c r="B107" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12617,7 +12617,7 @@
         <v>136227081</v>
       </c>
       <c r="B108" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12725,7 +12725,7 @@
         <v>136227083</v>
       </c>
       <c r="B109" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
         <v>136227085</v>
       </c>
       <c r="B110" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12941,7 +12941,7 @@
         <v>136227088</v>
       </c>
       <c r="B111" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -8447,7 +8447,7 @@
         <v>136227078</v>
       </c>
       <c r="B71" t="n">
-        <v>85375</v>
+        <v>85379</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8473,6 +8473,9 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
@@ -8527,6 +8530,11 @@
           <t>12:17</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Hittades under mykologiveckan 2026. Bekräftad av Cajsa Björken och Robin Isaksson.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8545,7 +8553,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136227066</v>
       </c>
       <c r="B4" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1461,7 +1461,7 @@
         <v>136203730</v>
       </c>
       <c r="B9" t="n">
-        <v>83428</v>
+        <v>83432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136179860</v>
       </c>
       <c r="B11" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92891</v>
+        <v>92897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136173199</v>
       </c>
       <c r="B14" t="n">
-        <v>81134</v>
+        <v>81138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135671126</v>
       </c>
       <c r="B19" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>136179836</v>
       </c>
       <c r="B20" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136179838</v>
       </c>
       <c r="B21" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136179876</v>
       </c>
       <c r="B22" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136227090</v>
       </c>
       <c r="B23" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
         <v>136240857</v>
       </c>
       <c r="B24" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136179865</v>
       </c>
       <c r="B27" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136227071</v>
       </c>
       <c r="B28" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
         <v>136240851</v>
       </c>
       <c r="B29" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136240854</v>
       </c>
       <c r="B30" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>136240856</v>
       </c>
       <c r="B31" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>135671135</v>
       </c>
       <c r="B33" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>136179832</v>
       </c>
       <c r="B34" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136179864</v>
       </c>
       <c r="B35" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>136179866</v>
       </c>
       <c r="B36" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>136179873</v>
       </c>
       <c r="B37" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136179874</v>
       </c>
       <c r="B38" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136219638</v>
       </c>
       <c r="B39" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136219642</v>
       </c>
       <c r="B40" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>136219649</v>
       </c>
       <c r="B41" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136227067</v>
       </c>
       <c r="B42" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5275,7 +5275,7 @@
         <v>136240852</v>
       </c>
       <c r="B43" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136240863</v>
       </c>
       <c r="B44" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136240866</v>
       </c>
       <c r="B45" t="n">
-        <v>75533</v>
+        <v>75537</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>136179859</v>
       </c>
       <c r="B46" t="n">
-        <v>80329</v>
+        <v>80333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>136179834</v>
       </c>
       <c r="B49" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>136179862</v>
       </c>
       <c r="B50" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136227069</v>
       </c>
       <c r="B51" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100573</v>
+        <v>100584</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100573</v>
+        <v>100584</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100573</v>
+        <v>100584</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100573</v>
+        <v>100584</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>136225509</v>
       </c>
       <c r="B57" t="n">
-        <v>87665</v>
+        <v>87671</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>136179861</v>
       </c>
       <c r="B61" t="n">
-        <v>78808</v>
+        <v>78812</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>136179833</v>
       </c>
       <c r="B63" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>136227075</v>
       </c>
       <c r="B64" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7990,7 +7990,7 @@
         <v>136219658</v>
       </c>
       <c r="B67" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8675,7 +8675,7 @@
         <v>136179840</v>
       </c>
       <c r="B73" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>136240864</v>
       </c>
       <c r="B74" t="n">
-        <v>80585</v>
+        <v>80589</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>136179844</v>
       </c>
       <c r="B76" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>136198395</v>
       </c>
       <c r="B77" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>136203727</v>
       </c>
       <c r="B78" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>136227076</v>
       </c>
       <c r="B79" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
         <v>136227082</v>
       </c>
       <c r="B80" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9575,7 +9575,7 @@
         <v>136227084</v>
       </c>
       <c r="B81" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9687,7 +9687,7 @@
         <v>136227086</v>
       </c>
       <c r="B82" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9799,7 +9799,7 @@
         <v>136240855</v>
       </c>
       <c r="B83" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>136240860</v>
       </c>
       <c r="B84" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>136179845</v>
       </c>
       <c r="B85" t="n">
-        <v>75466</v>
+        <v>75470</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>136179846</v>
       </c>
       <c r="B86" t="n">
-        <v>75466</v>
+        <v>75470</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>136179837</v>
       </c>
       <c r="B89" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>136179841</v>
       </c>
       <c r="B90" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>136179851</v>
       </c>
       <c r="B91" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>136179857</v>
       </c>
       <c r="B92" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136203725</v>
       </c>
       <c r="B93" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>136227070</v>
       </c>
       <c r="B94" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11169,7 +11169,7 @@
         <v>136227073</v>
       </c>
       <c r="B95" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11281,7 +11281,7 @@
         <v>136240853</v>
       </c>
       <c r="B96" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>136240858</v>
       </c>
       <c r="B97" t="n">
-        <v>75468</v>
+        <v>75472</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>136179843</v>
       </c>
       <c r="B98" t="n">
-        <v>80521</v>
+        <v>80525</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>136219661</v>
       </c>
       <c r="B99" t="n">
-        <v>80521</v>
+        <v>80525</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>136219654</v>
       </c>
       <c r="B100" t="n">
-        <v>79922</v>
+        <v>79926</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>136227089</v>
       </c>
       <c r="B101" t="n">
-        <v>79922</v>
+        <v>79926</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11975,7 +11975,7 @@
         <v>136240859</v>
       </c>
       <c r="B102" t="n">
-        <v>79922</v>
+        <v>79926</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136179850</v>
       </c>
       <c r="B103" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>136179852</v>
       </c>
       <c r="B104" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>136179854</v>
       </c>
       <c r="B105" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>136202366</v>
       </c>
       <c r="B106" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>136227080</v>
       </c>
       <c r="B107" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12625,7 +12625,7 @@
         <v>136227081</v>
       </c>
       <c r="B108" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12733,7 +12733,7 @@
         <v>136227083</v>
       </c>
       <c r="B109" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12841,7 +12841,7 @@
         <v>136227085</v>
       </c>
       <c r="B110" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12949,7 +12949,7 @@
         <v>136227088</v>
       </c>
       <c r="B111" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Erica Hästdahl, Alexander Singer, Uno Skog, Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136227066</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136203730</v>
       </c>
       <c r="B9" t="n">
-        <v>83432</v>
+        <v>83438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136179860</v>
       </c>
       <c r="B11" t="n">
-        <v>78813</v>
+        <v>78819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92897</v>
+        <v>92904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136173199</v>
       </c>
       <c r="B14" t="n">
-        <v>81138</v>
+        <v>81144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135671126</v>
       </c>
       <c r="B19" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>136179836</v>
       </c>
       <c r="B20" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136179838</v>
       </c>
       <c r="B21" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136179876</v>
       </c>
       <c r="B22" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136227090</v>
       </c>
       <c r="B23" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136240857</v>
       </c>
       <c r="B24" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136179865</v>
       </c>
       <c r="B27" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136227071</v>
       </c>
       <c r="B28" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136240851</v>
       </c>
       <c r="B29" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136240854</v>
       </c>
       <c r="B30" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>136240856</v>
       </c>
       <c r="B31" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>135671135</v>
       </c>
       <c r="B33" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>136179832</v>
       </c>
       <c r="B34" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136179864</v>
       </c>
       <c r="B35" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>136179866</v>
       </c>
       <c r="B36" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>136179873</v>
       </c>
       <c r="B37" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136179874</v>
       </c>
       <c r="B38" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136219638</v>
       </c>
       <c r="B39" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136219642</v>
       </c>
       <c r="B40" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>136219649</v>
       </c>
       <c r="B41" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136227067</v>
       </c>
       <c r="B42" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>136240852</v>
       </c>
       <c r="B43" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136240863</v>
       </c>
       <c r="B44" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136240866</v>
       </c>
       <c r="B45" t="n">
-        <v>75537</v>
+        <v>75543</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>136179859</v>
       </c>
       <c r="B46" t="n">
-        <v>80333</v>
+        <v>80339</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>136179834</v>
       </c>
       <c r="B49" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>136179862</v>
       </c>
       <c r="B50" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136227069</v>
       </c>
       <c r="B51" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100584</v>
+        <v>100597</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100584</v>
+        <v>100597</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100584</v>
+        <v>100597</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100584</v>
+        <v>100597</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>136225509</v>
       </c>
       <c r="B57" t="n">
-        <v>87671</v>
+        <v>87678</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>136179861</v>
       </c>
       <c r="B61" t="n">
-        <v>78812</v>
+        <v>78818</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>136179833</v>
       </c>
       <c r="B63" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>136227075</v>
       </c>
       <c r="B64" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136219658</v>
       </c>
       <c r="B67" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>136227091</v>
       </c>
       <c r="B69" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>136227078</v>
       </c>
       <c r="B71" t="n">
-        <v>85379</v>
+        <v>85386</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136179840</v>
       </c>
       <c r="B73" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>136240864</v>
       </c>
       <c r="B74" t="n">
-        <v>80589</v>
+        <v>80595</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>136179844</v>
       </c>
       <c r="B76" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>136198395</v>
       </c>
       <c r="B77" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>136203727</v>
       </c>
       <c r="B78" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>136227076</v>
       </c>
       <c r="B79" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>136227082</v>
       </c>
       <c r="B80" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136227084</v>
       </c>
       <c r="B81" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>136227086</v>
       </c>
       <c r="B82" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>136240855</v>
       </c>
       <c r="B83" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>136240860</v>
       </c>
       <c r="B84" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>136179845</v>
       </c>
       <c r="B85" t="n">
-        <v>75470</v>
+        <v>75476</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>136179846</v>
       </c>
       <c r="B86" t="n">
-        <v>75470</v>
+        <v>75476</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>136179837</v>
       </c>
       <c r="B89" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>136179841</v>
       </c>
       <c r="B90" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>136179851</v>
       </c>
       <c r="B91" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>136179857</v>
       </c>
       <c r="B92" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136203725</v>
       </c>
       <c r="B93" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>136227070</v>
       </c>
       <c r="B94" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>136227073</v>
       </c>
       <c r="B95" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136240853</v>
       </c>
       <c r="B96" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>136240858</v>
       </c>
       <c r="B97" t="n">
-        <v>75472</v>
+        <v>75478</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>136179843</v>
       </c>
       <c r="B98" t="n">
-        <v>80525</v>
+        <v>80531</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>136219661</v>
       </c>
       <c r="B99" t="n">
-        <v>80525</v>
+        <v>80531</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>136219654</v>
       </c>
       <c r="B100" t="n">
-        <v>79926</v>
+        <v>79932</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>136227089</v>
       </c>
       <c r="B101" t="n">
-        <v>79926</v>
+        <v>79932</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>136240859</v>
       </c>
       <c r="B102" t="n">
-        <v>79926</v>
+        <v>79932</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136179850</v>
       </c>
       <c r="B103" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>136179852</v>
       </c>
       <c r="B104" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>136179854</v>
       </c>
       <c r="B105" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>136202366</v>
       </c>
       <c r="B106" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>136227080</v>
       </c>
       <c r="B107" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>136227081</v>
       </c>
       <c r="B108" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>136227083</v>
       </c>
       <c r="B109" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>136227085</v>
       </c>
       <c r="B110" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>136227088</v>
       </c>
       <c r="B111" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92904</v>
+        <v>92905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100597</v>
+        <v>100598</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100597</v>
+        <v>100598</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100597</v>
+        <v>100598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100597</v>
+        <v>100598</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136227066</v>
       </c>
       <c r="B4" t="n">
-        <v>79541</v>
+        <v>79554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136203730</v>
       </c>
       <c r="B9" t="n">
-        <v>83438</v>
+        <v>83451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136179860</v>
       </c>
       <c r="B11" t="n">
-        <v>78819</v>
+        <v>78832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92905</v>
+        <v>92918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136173199</v>
       </c>
       <c r="B14" t="n">
-        <v>81144</v>
+        <v>81157</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135671126</v>
       </c>
       <c r="B19" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>136179836</v>
       </c>
       <c r="B20" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136179838</v>
       </c>
       <c r="B21" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136179876</v>
       </c>
       <c r="B22" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136227090</v>
       </c>
       <c r="B23" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136240857</v>
       </c>
       <c r="B24" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136179865</v>
       </c>
       <c r="B27" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136227071</v>
       </c>
       <c r="B28" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136240851</v>
       </c>
       <c r="B29" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136240854</v>
       </c>
       <c r="B30" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>136240856</v>
       </c>
       <c r="B31" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>135671135</v>
       </c>
       <c r="B33" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>136179832</v>
       </c>
       <c r="B34" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136179864</v>
       </c>
       <c r="B35" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>136179866</v>
       </c>
       <c r="B36" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>136179873</v>
       </c>
       <c r="B37" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136179874</v>
       </c>
       <c r="B38" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136219638</v>
       </c>
       <c r="B39" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136219642</v>
       </c>
       <c r="B40" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>136219649</v>
       </c>
       <c r="B41" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136227067</v>
       </c>
       <c r="B42" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>136240852</v>
       </c>
       <c r="B43" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136240863</v>
       </c>
       <c r="B44" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136240866</v>
       </c>
       <c r="B45" t="n">
-        <v>75543</v>
+        <v>75556</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>136179859</v>
       </c>
       <c r="B46" t="n">
-        <v>80339</v>
+        <v>80352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>136179834</v>
       </c>
       <c r="B49" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>136179862</v>
       </c>
       <c r="B50" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136227069</v>
       </c>
       <c r="B51" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100598</v>
+        <v>100611</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100598</v>
+        <v>100611</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100598</v>
+        <v>100611</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100598</v>
+        <v>100611</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>136225509</v>
       </c>
       <c r="B57" t="n">
-        <v>87678</v>
+        <v>87691</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>136179861</v>
       </c>
       <c r="B61" t="n">
-        <v>78818</v>
+        <v>78831</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>136179833</v>
       </c>
       <c r="B63" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>136227075</v>
       </c>
       <c r="B64" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136219658</v>
       </c>
       <c r="B67" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>136227091</v>
       </c>
       <c r="B69" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>136227078</v>
       </c>
       <c r="B71" t="n">
-        <v>85386</v>
+        <v>85399</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136179840</v>
       </c>
       <c r="B73" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>136240864</v>
       </c>
       <c r="B74" t="n">
-        <v>80595</v>
+        <v>80608</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>136179844</v>
       </c>
       <c r="B76" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>136198395</v>
       </c>
       <c r="B77" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>136203727</v>
       </c>
       <c r="B78" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>136227076</v>
       </c>
       <c r="B79" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>136227082</v>
       </c>
       <c r="B80" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136227084</v>
       </c>
       <c r="B81" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>136227086</v>
       </c>
       <c r="B82" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>136240855</v>
       </c>
       <c r="B83" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>136240860</v>
       </c>
       <c r="B84" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>136179845</v>
       </c>
       <c r="B85" t="n">
-        <v>75476</v>
+        <v>75489</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>136179846</v>
       </c>
       <c r="B86" t="n">
-        <v>75476</v>
+        <v>75489</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>136179837</v>
       </c>
       <c r="B89" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>136179841</v>
       </c>
       <c r="B90" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>136179851</v>
       </c>
       <c r="B91" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>136179857</v>
       </c>
       <c r="B92" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136203725</v>
       </c>
       <c r="B93" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>136227070</v>
       </c>
       <c r="B94" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>136227073</v>
       </c>
       <c r="B95" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136240853</v>
       </c>
       <c r="B96" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>136240858</v>
       </c>
       <c r="B97" t="n">
-        <v>75478</v>
+        <v>75491</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>136179843</v>
       </c>
       <c r="B98" t="n">
-        <v>80531</v>
+        <v>80544</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>136219661</v>
       </c>
       <c r="B99" t="n">
-        <v>80531</v>
+        <v>80544</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>136219654</v>
       </c>
       <c r="B100" t="n">
-        <v>79932</v>
+        <v>79945</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>136227089</v>
       </c>
       <c r="B101" t="n">
-        <v>79932</v>
+        <v>79945</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>136240859</v>
       </c>
       <c r="B102" t="n">
-        <v>79932</v>
+        <v>79945</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136179850</v>
       </c>
       <c r="B103" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>136179852</v>
       </c>
       <c r="B104" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>136179854</v>
       </c>
       <c r="B105" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>136202366</v>
       </c>
       <c r="B106" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>136227080</v>
       </c>
       <c r="B107" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>136227081</v>
       </c>
       <c r="B108" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>136227083</v>
       </c>
       <c r="B109" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>136227085</v>
       </c>
       <c r="B110" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>136227088</v>
       </c>
       <c r="B111" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136227066</v>
       </c>
       <c r="B4" t="n">
-        <v>79554</v>
+        <v>79555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136203730</v>
       </c>
       <c r="B9" t="n">
-        <v>83451</v>
+        <v>83452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136179860</v>
       </c>
       <c r="B11" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136198394</v>
       </c>
       <c r="B13" t="n">
-        <v>92918</v>
+        <v>92919</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136173199</v>
       </c>
       <c r="B14" t="n">
-        <v>81157</v>
+        <v>81158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>136203732</v>
       </c>
       <c r="B15" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>135671126</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>136179836</v>
       </c>
       <c r="B20" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>136179838</v>
       </c>
       <c r="B21" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136179876</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>136227090</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>136240857</v>
       </c>
       <c r="B24" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136179865</v>
       </c>
       <c r="B27" t="n">
-        <v>83465</v>
+        <v>83466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136227071</v>
       </c>
       <c r="B28" t="n">
-        <v>83465</v>
+        <v>83466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136240851</v>
       </c>
       <c r="B29" t="n">
-        <v>83465</v>
+        <v>83466</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>136240854</v>
       </c>
       <c r="B30" t="n">
-        <v>83465</v>
+        <v>83466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>136240856</v>
       </c>
       <c r="B31" t="n">
-        <v>83465</v>
+        <v>83466</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>135671135</v>
       </c>
       <c r="B33" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>136179832</v>
       </c>
       <c r="B34" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136179864</v>
       </c>
       <c r="B35" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>136179866</v>
       </c>
       <c r="B36" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>136179873</v>
       </c>
       <c r="B37" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136179874</v>
       </c>
       <c r="B38" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136219638</v>
       </c>
       <c r="B39" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136219642</v>
       </c>
       <c r="B40" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>136219649</v>
       </c>
       <c r="B41" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136227067</v>
       </c>
       <c r="B42" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>136240852</v>
       </c>
       <c r="B43" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136240863</v>
       </c>
       <c r="B44" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136240866</v>
       </c>
       <c r="B45" t="n">
-        <v>75556</v>
+        <v>75557</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>136179859</v>
       </c>
       <c r="B46" t="n">
-        <v>80352</v>
+        <v>80353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>136179834</v>
       </c>
       <c r="B49" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>136179862</v>
       </c>
       <c r="B50" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136227069</v>
       </c>
       <c r="B51" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>135669073</v>
       </c>
       <c r="B52" t="n">
-        <v>100611</v>
+        <v>100612</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>135669652</v>
       </c>
       <c r="B53" t="n">
-        <v>100611</v>
+        <v>100612</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>136179870</v>
       </c>
       <c r="B54" t="n">
-        <v>100611</v>
+        <v>100612</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136240862</v>
       </c>
       <c r="B55" t="n">
-        <v>100611</v>
+        <v>100612</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>136225509</v>
       </c>
       <c r="B57" t="n">
-        <v>87691</v>
+        <v>87692</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>136179861</v>
       </c>
       <c r="B61" t="n">
-        <v>78831</v>
+        <v>78832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>136179833</v>
       </c>
       <c r="B63" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>136227075</v>
       </c>
       <c r="B64" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136219658</v>
       </c>
       <c r="B67" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>136227078</v>
       </c>
       <c r="B71" t="n">
-        <v>85399</v>
+        <v>85400</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136179840</v>
       </c>
       <c r="B73" t="n">
-        <v>80538</v>
+        <v>80539</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>136240864</v>
       </c>
       <c r="B74" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>136179844</v>
       </c>
       <c r="B76" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>136198395</v>
       </c>
       <c r="B77" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>136203727</v>
       </c>
       <c r="B78" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>136227076</v>
       </c>
       <c r="B79" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>136227082</v>
       </c>
       <c r="B80" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136227084</v>
       </c>
       <c r="B81" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>136227086</v>
       </c>
       <c r="B82" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>136240855</v>
       </c>
       <c r="B83" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>136240860</v>
       </c>
       <c r="B84" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>136179845</v>
       </c>
       <c r="B85" t="n">
-        <v>75489</v>
+        <v>75490</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>136179846</v>
       </c>
       <c r="B86" t="n">
-        <v>75489</v>
+        <v>75490</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>136179837</v>
       </c>
       <c r="B89" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>136179841</v>
       </c>
       <c r="B90" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>136179851</v>
       </c>
       <c r="B91" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>136179857</v>
       </c>
       <c r="B92" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136203725</v>
       </c>
       <c r="B93" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>136227070</v>
       </c>
       <c r="B94" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>136227073</v>
       </c>
       <c r="B95" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136240853</v>
       </c>
       <c r="B96" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>136240858</v>
       </c>
       <c r="B97" t="n">
-        <v>75491</v>
+        <v>75492</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>136179843</v>
       </c>
       <c r="B98" t="n">
-        <v>80544</v>
+        <v>80545</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>136219661</v>
       </c>
       <c r="B99" t="n">
-        <v>80544</v>
+        <v>80545</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>136219654</v>
       </c>
       <c r="B100" t="n">
-        <v>79945</v>
+        <v>79946</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>136227089</v>
       </c>
       <c r="B101" t="n">
-        <v>79945</v>
+        <v>79946</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>136240859</v>
       </c>
       <c r="B102" t="n">
-        <v>79945</v>
+        <v>79946</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136179850</v>
       </c>
       <c r="B103" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>136179852</v>
       </c>
       <c r="B104" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>136179854</v>
       </c>
       <c r="B105" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>136202366</v>
       </c>
       <c r="B106" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>136227080</v>
       </c>
       <c r="B107" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>136227081</v>
       </c>
       <c r="B108" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>136227083</v>
       </c>
       <c r="B109" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>136227085</v>
       </c>
       <c r="B110" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>136227088</v>
       </c>
       <c r="B111" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
